--- a/StructureDefinition-heartland-monitoring-track-ext.xlsx
+++ b/StructureDefinition-heartland-monitoring-track-ext.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-monitoring-track-ext</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-monitoring-track-ext</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-track-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-track-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -699,7 +699,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.23046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.96484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.1015625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.91015625" customWidth="true" bestFit="true"/>
